--- a/data/processed/positivacao/2022-12_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2022-12_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25621,7 +25621,7 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B973" t="inlineStr"/>
@@ -37025,7 +37025,7 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr"/>
@@ -66151,7 +66151,7 @@
     <row r="2533">
       <c r="A2533" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2533" t="inlineStr"/>
@@ -67822,12 +67822,12 @@
       <c r="A2598" t="inlineStr"/>
       <c r="B2598" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 8 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 19.113,32
+          <t>Vendedor 1 - VENDEDOR 01: positivou 8 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 19.113,32
 Vendedor 18 - LOJA: positivou 126 cliente(s), não positivou 740 cliente(s) - Total vendido: R$ 101.655,37
-Vendedor 3 - FERNANDA: positivou 112 cliente(s), não positivou 326 cliente(s) - Total vendido: R$ 156.499,55
-Vendedor 4 - DANIELA: positivou 69 cliente(s), não positivou 596 cliente(s) - Total vendido: R$ 47.595,59
+Vendedor 3 - VENDEDOR 03: positivou 112 cliente(s), não positivou 326 cliente(s) - Total vendido: R$ 156.499,55
+Vendedor 4 - VENDEDOR 04: positivou 69 cliente(s), não positivou 596 cliente(s) - Total vendido: R$ 47.595,59
 Vendedor 5 - SITE: positivou 11 cliente(s), não positivou 443 cliente(s) - Total vendido: R$ 2.837,52
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2598" t="inlineStr"/>
